--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104709_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104709_W28.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7379</v>
+        <v>3.4223</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7262</v>
+        <v>5.2706</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9883</v>
+        <v>-1.8482</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.7302</v>
+        <v>-1.7239</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.4558</v>
+        <v>-1.467</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2744</v>
+        <v>-0.2569</v>
       </c>
       <c r="J2" t="n">
-        <v>0.025</v>
+        <v>-0.0119</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.8782</v>
+        <v>-1.911</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9032</v>
+        <v>1.8991</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7551</v>
+        <v>-1.712</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4224</v>
+        <v>0.444</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1776</v>
+        <v>-2.156</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>0.483</v>
+        <v>0.1754</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9164</v>
+        <v>0.5196</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4334</v>
+        <v>-0.3442</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5314</v>
+        <v>4.5157</v>
       </c>
       <c r="W2" t="n">
-        <v>5.2385</v>
+        <v>5.2182</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.29</v>
+        <v>2.9002</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4624</v>
+        <v>2.2819</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8276</v>
+        <v>0.6183</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2377</v>
+        <v>3.2179</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1213</v>
+        <v>1.112</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1163</v>
+        <v>2.1059</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7193</v>
+        <v>3.6696</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4462</v>
+        <v>0.4234</v>
       </c>
       <c r="L3" t="n">
-        <v>3.273</v>
+        <v>3.2462</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4816</v>
+        <v>-0.4518</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6751</v>
+        <v>0.6886</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1567</v>
+        <v>-1.1403</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8897</v>
+        <v>1.5262</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5293</v>
+        <v>0.4153</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3604</v>
+        <v>1.1109</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1568</v>
+        <v>-1.1609</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. TOMAS</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4169</v>
+        <v>2.7989</v>
       </c>
       <c r="E4" t="n">
-        <v>1.127</v>
+        <v>3.1081</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2899</v>
+        <v>-0.3092</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1193</v>
+        <v>1.4238</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4747</v>
+        <v>2.8953</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6446</v>
+        <v>-1.4715</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2661</v>
+        <v>2.8668</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0346</v>
+        <v>2.4649</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2315</v>
+        <v>0.4019</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8532</v>
+        <v>-1.443</v>
       </c>
       <c r="N4" t="n">
-        <v>0.44</v>
+        <v>0.4305</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4132</v>
+        <v>-1.8734</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1561</v>
+        <v>0.7409</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1391</v>
+        <v>0.5177</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0169</v>
+        <v>0.2232</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>P. TOMAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3773</v>
+        <v>2.416</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7065</v>
+        <v>1.2423</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3292</v>
+        <v>1.1736</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4238</v>
+        <v>2.1255</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9004</v>
+        <v>0.4794</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4767</v>
+        <v>1.6461</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8841</v>
+        <v>1.2633</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4763</v>
+        <v>0.0345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4078</v>
+        <v>1.2288</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4603</v>
+        <v>0.8622</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4241</v>
+        <v>0.4449</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8844</v>
+        <v>0.4173</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3145</v>
+        <v>-0.1648</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0907</v>
+        <v>-0.021</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2238</v>
+        <v>-0.1438</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6978</v>
+        <v>1.0696</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1234</v>
+        <v>1.5216</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4256</v>
+        <v>-0.452</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6697</v>
+        <v>1.6863</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1254</v>
+        <v>2.1281</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4557</v>
+        <v>-0.4418</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5941</v>
+        <v>1.5801</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4821</v>
+        <v>1.4684</v>
       </c>
       <c r="L6" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0757</v>
+        <v>0.1062</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6433</v>
+        <v>0.6597</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5329</v>
+        <v>-0.1206</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7561</v>
+        <v>0.1691</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2232</v>
+        <v>-0.2898</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.276</v>
+        <v>0.0337</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1727</v>
+        <v>0.3926</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4487</v>
+        <v>-0.359</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1943</v>
+        <v>3.0193</v>
       </c>
       <c r="H7" t="n">
-        <v>4.0331</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8388</v>
+        <v>3.5914</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1696</v>
+        <v>3.0711</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3421</v>
+        <v>-1.3897</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.1725</v>
+        <v>4.4608</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0247</v>
+        <v>-0.0518</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.8176</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6663</v>
+        <v>-0.8694</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4537</v>
+        <v>-2.7316</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>0.715</v>
+        <v>-0.7093</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4567</v>
+        <v>0.0531</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2583</v>
+        <v>-0.7625</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4652</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2368</v>
+        <v>1.2181</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2283</v>
+        <v>-1.8586</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0115</v>
+        <v>1.192</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5817</v>
+        <v>4.0297</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5931</v>
+        <v>-2.8377</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0931</v>
+        <v>1.144</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3822</v>
+        <v>3.3267</v>
       </c>
       <c r="L8" t="n">
-        <v>4.4753</v>
+        <v>-2.1827</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.0481</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8006</v>
+        <v>0.703</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8822</v>
+        <v>-0.6549</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.722</v>
+        <v>-0.4553</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2083</v>
+        <v>0.3463</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6079</v>
+        <v>0.5294</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6004</v>
+        <v>-0.183</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1659</v>
+        <v>-1.3413</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3833</v>
+        <v>-1.6326</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2174</v>
+        <v>0.2914</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6795</v>
+        <v>-1.6827</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1255</v>
+        <v>-0.129</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.554</v>
+        <v>-1.5537</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4559</v>
+        <v>-1.4698</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2236</v>
+        <v>-0.2129</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2867</v>
+        <v>0.1138</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2994</v>
+        <v>0.0648</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0127</v>
+        <v>0.049</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7258</v>
+        <v>-1.4765</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7834</v>
+        <v>-0.6687</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9423</v>
+        <v>-0.8078</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3737</v>
+        <v>-1.3673</v>
       </c>
       <c r="H10" t="n">
-        <v>0.023</v>
+        <v>0.0284</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3967</v>
+        <v>-1.3957</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6625</v>
+        <v>-0.6662</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7113</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.352</v>
+        <v>-0.1092</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.121</v>
+        <v>-0.0024</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2311</v>
+        <v>-0.1067</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8084</v>
+        <v>-1.9101</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2681</v>
+        <v>-1.7642</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5403</v>
+        <v>-0.146</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1081</v>
+        <v>-1.1076</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2552</v>
+        <v>-0.2665</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8529</v>
+        <v>-0.8411</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4928</v>
+        <v>-0.5108</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6793</v>
+        <v>-0.697</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6153</v>
+        <v>-0.5968</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7948</v>
+        <v>0.7014</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9467</v>
+        <v>0.4782</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1518</v>
+        <v>0.2232</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6608</v>
+        <v>-4.5085</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4857</v>
+        <v>-4.7522</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1751</v>
+        <v>0.2437</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.1808</v>
+        <v>-7.1835</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6262</v>
+        <v>-0.6261</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.5546</v>
+        <v>-6.5574</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.0465</v>
+        <v>-6.0872</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7659</v>
+        <v>-0.7831</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.2806</v>
+        <v>-5.3041</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1343</v>
+        <v>-1.0963</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1397</v>
+        <v>0.157</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.274</v>
+        <v>-1.2533</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8656</v>
+        <v>0.2881</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4657</v>
+        <v>0.3154</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3999</v>
+        <v>-0.0273</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.417799999999998</v>
+        <v>2.7637</v>
       </c>
       <c r="E13" t="n">
-        <v>6.160900000000002</v>
+        <v>6.217499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.742899999999999</v>
+        <v>-3.4538</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4160000000000004</v>
+        <v>-0.4002000000000017</v>
       </c>
       <c r="H13" t="n">
-        <v>7.633499999999999</v>
+        <v>7.612199999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.049799999999999</v>
+        <v>-8.0124</v>
       </c>
       <c r="J13" t="n">
-        <v>5.0936</v>
+        <v>4.849000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2418</v>
+        <v>3.095499999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.851900000000001</v>
+        <v>1.7535</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.509499999999999</v>
+        <v>-5.2492</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3917</v>
+        <v>4.5168</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.901400000000002</v>
+        <v>-9.765700000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2074</v>
+        <v>-10.2434</v>
       </c>
       <c r="R13" t="n">
-        <v>7.9392</v>
+        <v>7.9672</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4346</v>
+        <v>2.7882</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6616</v>
+        <v>3.0392</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2268999999999999</v>
+        <v>-0.2510000000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6676</v>
+        <v>2.652299999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>8.613099999999999</v>
+        <v>8.572900000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.9455</v>
+        <v>-5.920600000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0689</v>
+        <v>4.0161</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2222</v>
+        <v>2.3204</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8467</v>
+        <v>1.6957</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5231</v>
+        <v>4.5352</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0877</v>
+        <v>0.1053</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4354</v>
+        <v>4.4299</v>
       </c>
       <c r="J14" t="n">
-        <v>2.688</v>
+        <v>2.667</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5667</v>
+        <v>2.5463</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8352</v>
+        <v>1.8682</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O14" t="n">
-        <v>1.8687</v>
+        <v>1.8835</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2689</v>
+        <v>-0.3401</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2389</v>
+        <v>-0.1189</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.03</v>
+        <v>-0.2212</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4253</v>
+        <v>3.8234</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0872</v>
+        <v>4.647</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3381</v>
+        <v>-0.8236</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4763</v>
+        <v>5.3945</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0404</v>
+        <v>-0.1295</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4358</v>
+        <v>5.524</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7052</v>
+        <v>4.888</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3494</v>
+        <v>0.1304</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3558</v>
+        <v>4.7575</v>
       </c>
       <c r="M15" t="n">
-        <v>0.771</v>
+        <v>0.5065</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.2599</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08</v>
+        <v>0.7664</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1098</v>
+        <v>-1.2555</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2571</v>
+        <v>-0.5094</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3668</v>
+        <v>-0.7461</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7071</v>
+        <v>-0.3155</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3246</v>
+        <v>3.1327</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8907</v>
+        <v>2.1744</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5661</v>
+        <v>0.9583</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4125</v>
+        <v>4.4705</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1343</v>
+        <v>1.037</v>
       </c>
       <c r="I16" t="n">
-        <v>5.5468</v>
+        <v>3.4335</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9495</v>
+        <v>3.6777</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1519</v>
+        <v>0.334</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7976</v>
+        <v>3.3436</v>
       </c>
       <c r="M16" t="n">
-        <v>0.463</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2861</v>
+        <v>0.703</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7492</v>
+        <v>0.0898</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.7664</v>
+        <v>-0.18</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3368</v>
+        <v>-0.1375</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4297</v>
+        <v>-0.0425</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3214</v>
+        <v>-0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.9604</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7769</v>
+        <v>1.2871</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1319</v>
+        <v>0.5374</v>
       </c>
       <c r="F17" t="n">
-        <v>0.645</v>
+        <v>0.7497</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1042</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2813</v>
+        <v>-2.2832</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3855</v>
+        <v>2.3615</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4652</v>
+        <v>-0.5281</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.2001</v>
+        <v>-2.2245</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7349</v>
+        <v>1.6965</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5693</v>
+        <v>0.6063</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0587</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0758</v>
+        <v>-0.5424</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4294</v>
+        <v>0.0458</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6463</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1912</v>
+        <v>0.4059</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8065</v>
+        <v>0.2102</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6153999999999999</v>
+        <v>0.1958</v>
       </c>
       <c r="G18" t="n">
-        <v>0.649</v>
+        <v>0.3931</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0866</v>
+        <v>0.0028</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5625</v>
+        <v>0.3903</v>
       </c>
       <c r="J18" t="n">
-        <v>1.608</v>
+        <v>0.0917</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3392</v>
+        <v>0.0172</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2688</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.959</v>
+        <v>0.3014</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2526</v>
+        <v>-0.0144</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7063</v>
+        <v>0.3159</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2207</v>
+        <v>0.0128</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1039</v>
+        <v>0.1184</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1167</v>
+        <v>-0.1057</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0969</v>
+        <v>-0.2332</v>
       </c>
       <c r="E19" t="n">
-        <v>0.092</v>
+        <v>0.0839</v>
       </c>
       <c r="F19" t="n">
-        <v>0.005</v>
+        <v>-0.3171</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3906</v>
+        <v>0.6524</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0014</v>
+        <v>0.0862</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3892</v>
+        <v>0.5662</v>
       </c>
       <c r="J19" t="n">
-        <v>0.092</v>
+        <v>1.5968</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0173</v>
+        <v>0.3308</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>1.2661</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2986</v>
+        <v>-0.9444</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0159</v>
+        <v>-0.2446</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3145</v>
+        <v>-0.6998</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2937</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.3992</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2937</v>
+        <v>0.3997</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,22 +1969,22 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1996,13 +1996,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3258</v>
+        <v>-1.4117</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5454</v>
+        <v>-0.6706</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7804</v>
+        <v>-0.7411</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4657</v>
+        <v>-2.4695</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3462</v>
+        <v>-1.3524</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9839</v>
+        <v>-0.9932</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9839</v>
+        <v>-0.9932</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4817</v>
+        <v>-1.4763</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4594</v>
+        <v>0.375</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4386</v>
+        <v>0.3227</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3868</v>
+        <v>-1.8525</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1503</v>
+        <v>-0.4384</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5371</v>
+        <v>-1.4141</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2333</v>
+        <v>-5.64</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4863</v>
+        <v>-3.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7196</v>
+        <v>-2.5295</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8429</v>
+        <v>-3.6181</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5817</v>
+        <v>-1.4726</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2612</v>
+        <v>-2.1455</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0762</v>
+        <v>-2.0219</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0954</v>
+        <v>-1.638</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9808</v>
+        <v>-0.384</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0073</v>
+        <v>-0.4612</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6684</v>
+        <v>-0.0887</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6611</v>
+        <v>-0.3725</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7071</v>
+        <v>3.1107</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7064</v>
+        <v>-1.896</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1706</v>
+        <v>-0.5706</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5359</v>
+        <v>-1.3254</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.6394</v>
+        <v>-0.2247</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1125</v>
+        <v>0.4854</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5269</v>
+        <v>-0.7101</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.5938</v>
+        <v>0.8327</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4586</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.1352</v>
+        <v>0.2607</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0457</v>
+        <v>-1.0574</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6539</v>
+        <v>-0.0866</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3918</v>
+        <v>-0.9708</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3185</v>
+        <v>-0.5135</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1452</v>
+        <v>-0.0375</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4637</v>
+        <v>-0.476</v>
       </c>
       <c r="V23" t="n">
-        <v>3.1173</v>
+        <v>-0.7025</v>
       </c>
       <c r="W23" t="n">
-        <v>3.278</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1973</v>
+        <v>-2.0317</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4162</v>
+        <v>-2.3156</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2189</v>
+        <v>0.2839</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3951</v>
+        <v>-0.3803</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9149</v>
+        <v>-0.908</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5198</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.154</v>
+        <v>-0.1665</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3779</v>
+        <v>-0.3899</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2411</v>
+        <v>-0.2138</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5371</v>
+        <v>-0.518</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.039</v>
+        <v>0.1892</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0061</v>
+        <v>0.1272</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0329</v>
+        <v>0.062</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3122</v>
+        <v>-6.4935</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5057</v>
+        <v>-2.5243</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8065</v>
+        <v>-3.9692</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.033</v>
+        <v>-6.0367</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5469</v>
+        <v>-1.5453</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.4861</v>
+        <v>-4.4914</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.1791</v>
+        <v>-3.1987</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9415</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.8539</v>
+        <v>-2.838</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.239</v>
+        <v>-2.2342</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4525</v>
+        <v>0.2669</v>
       </c>
       <c r="T25" t="n">
-        <v>0.127</v>
+        <v>0.1297</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3254</v>
+        <v>0.1372</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.417899999999998</v>
+        <v>-1.625799999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>3.7429</v>
+        <v>3.453799999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.1609</v>
+        <v>-5.079499999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4160000000000021</v>
+        <v>0.4004000000000003</v>
       </c>
       <c r="H26" t="n">
-        <v>-7.6337</v>
+        <v>-7.6123</v>
       </c>
       <c r="I26" t="n">
-        <v>8.0497</v>
+        <v>8.012599999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>5.509600000000001</v>
+        <v>5.2493</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.3918</v>
+        <v>-4.516499999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>9.901200000000003</v>
+        <v>9.765900000000002</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.0937</v>
+        <v>-4.849</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.2418</v>
+        <v>-3.0955</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.8518</v>
+        <v>-1.753400000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>2.268200000000001</v>
+        <v>2.2762</v>
       </c>
       <c r="Q26" t="n">
-        <v>-7.9391</v>
+        <v>-7.9671</v>
       </c>
       <c r="R26" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.4346</v>
+        <v>-1.6499</v>
       </c>
       <c r="T26" t="n">
-        <v>0.227</v>
+        <v>0.2510000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.6618</v>
+        <v>-1.901</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.6676</v>
+        <v>-2.6521</v>
       </c>
       <c r="W26" t="n">
-        <v>5.945500000000001</v>
+        <v>5.920599999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.613099999999999</v>
+        <v>-8.572899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104709_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104709_W28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.920600000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104709_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-8.572899999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
